--- a/output/roomself_excel/6470.xlsx
+++ b/output/roomself_excel/6470.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87283</v>
+        <v>129479</v>
       </c>
       <c r="D2" t="n">
-        <v>2384</v>
+        <v>2904</v>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="F2" t="n">
-        <v>288</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>82902</v>
+        <v>354876</v>
       </c>
       <c r="D3" t="n">
-        <v>2332</v>
+        <v>7016</v>
       </c>
       <c r="E3" t="n">
-        <v>246</v>
+        <v>961</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>867</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70096</v>
+        <v>87283</v>
       </c>
       <c r="D4" t="n">
-        <v>2180</v>
+        <v>2384</v>
       </c>
       <c r="E4" t="n">
-        <v>208</v>
+        <v>366</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>651191</v>
+        <v>82902</v>
       </c>
       <c r="D5" t="n">
-        <v>11116</v>
+        <v>2332</v>
       </c>
       <c r="E5" t="n">
-        <v>976</v>
+        <v>246</v>
       </c>
       <c r="F5" t="n">
-        <v>867</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -554,17 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36066</v>
+        <v>70096</v>
       </c>
       <c r="D6" t="n">
-        <v>1556</v>
+        <v>2180</v>
       </c>
       <c r="E6" t="n">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>288192</v>
+        <v>36066</v>
       </c>
       <c r="D8" t="n">
-        <v>4728</v>
+        <v>1556</v>
       </c>
       <c r="E8" t="n">
-        <v>877</v>
+        <v>222</v>
       </c>
       <c r="F8" t="n">
-        <v>705</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -620,17 +620,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75012</v>
+        <v>18850</v>
       </c>
       <c r="D9" t="n">
-        <v>2228</v>
+        <v>1100</v>
       </c>
       <c r="E9" t="n">
-        <v>329</v>
+        <v>145</v>
       </c>
       <c r="F9" t="n">
         <v>34</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>123866</v>
+        <v>104930</v>
       </c>
       <c r="D10" t="n">
-        <v>3388</v>
+        <v>3156</v>
       </c>
       <c r="E10" t="n">
-        <v>877</v>
+        <v>464</v>
       </c>
       <c r="F10" t="n">
-        <v>207</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18850</v>
+        <v>166836</v>
       </c>
       <c r="D11" t="n">
-        <v>1100</v>
+        <v>6148</v>
       </c>
       <c r="E11" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>104930</v>
+        <v>123866</v>
       </c>
       <c r="D12" t="n">
-        <v>3156</v>
+        <v>3388</v>
       </c>
       <c r="E12" t="n">
-        <v>464</v>
+        <v>877</v>
       </c>
       <c r="F12" t="n">
-        <v>417</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43093</v>
+        <v>34209</v>
       </c>
       <c r="D13" t="n">
-        <v>1704</v>
+        <v>1480</v>
       </c>
       <c r="E13" t="n">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="F13" t="n">
-        <v>241</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37410</v>
+        <v>52334</v>
       </c>
       <c r="D14" t="n">
-        <v>1612</v>
+        <v>1860</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52334</v>
+        <v>288192</v>
       </c>
       <c r="D15" t="n">
-        <v>1860</v>
+        <v>4728</v>
       </c>
       <c r="E15" t="n">
-        <v>292</v>
+        <v>877</v>
       </c>
       <c r="F15" t="n">
-        <v>222</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>186117</v>
+        <v>129525</v>
       </c>
       <c r="D16" t="n">
-        <v>3904</v>
+        <v>2984</v>
       </c>
       <c r="E16" t="n">
-        <v>877</v>
+        <v>240</v>
       </c>
       <c r="F16" t="n">
-        <v>368</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>129525</v>
+        <v>75012</v>
       </c>
       <c r="D17" t="n">
-        <v>2984</v>
+        <v>2228</v>
       </c>
       <c r="E17" t="n">
-        <v>240</v>
+        <v>329</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>122038</v>
+        <v>43093</v>
       </c>
       <c r="D18" t="n">
-        <v>2804</v>
+        <v>1704</v>
       </c>
       <c r="E18" t="n">
-        <v>582</v>
+        <v>248</v>
       </c>
       <c r="F18" t="n">
-        <v>424</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,64 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>34209</v>
+        <v>37410</v>
       </c>
       <c r="D19" t="n">
-        <v>1480</v>
+        <v>1612</v>
       </c>
       <c r="E19" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>186117</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3904</v>
+      </c>
+      <c r="E20" t="n">
+        <v>368</v>
+      </c>
+      <c r="F20" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>122038</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2804</v>
+      </c>
+      <c r="E21" t="n">
+        <v>582</v>
+      </c>
+      <c r="F21" t="n">
+        <v>424</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/6470.xlsx
+++ b/output/roomself_excel/6470.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,26 @@
       <c r="D2" t="n">
         <v>2904</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>318</v>
       </c>
-      <c r="F2" t="n">
-        <v>29</v>
-      </c>
+      <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +561,49 @@
       <c r="D3" t="n">
         <v>7016</v>
       </c>
-      <c r="E3" t="n">
-        <v>961</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>867</v>
+        <v>958</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>407</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>210</v>
+      </c>
+      <c r="M3" t="n">
+        <v>35</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>367</v>
+      </c>
+      <c r="P3" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +621,34 @@
       <c r="D4" t="n">
         <v>2384</v>
       </c>
-      <c r="E4" t="n">
-        <v>366</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>288</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>337</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +665,26 @@
       <c r="D5" t="n">
         <v>2332</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>246</v>
       </c>
-      <c r="F5" t="n">
-        <v>29</v>
-      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +701,26 @@
       <c r="D6" t="n">
         <v>2180</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>208</v>
       </c>
-      <c r="F6" t="n">
-        <v>29</v>
-      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +737,34 @@
       <c r="D7" t="n">
         <v>3480</v>
       </c>
-      <c r="E7" t="n">
-        <v>594</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>262</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="G7" t="n">
+        <v>29</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>565</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +781,26 @@
       <c r="D8" t="n">
         <v>1556</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>222</v>
       </c>
-      <c r="F8" t="n">
-        <v>29</v>
-      </c>
+      <c r="G8" t="n">
+        <v>29</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +817,26 @@
       <c r="D9" t="n">
         <v>1100</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>145</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>34</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +853,42 @@
       <c r="D10" t="n">
         <v>3156</v>
       </c>
-      <c r="E10" t="n">
-        <v>464</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>417</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>177</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>202</v>
+      </c>
+      <c r="M10" t="n">
+        <v>29</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +905,26 @@
       <c r="D11" t="n">
         <v>6148</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>181</v>
       </c>
-      <c r="F11" t="n">
-        <v>29</v>
-      </c>
+      <c r="G11" t="n">
+        <v>29</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +941,26 @@
       <c r="D12" t="n">
         <v>3388</v>
       </c>
-      <c r="E12" t="n">
-        <v>877</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>207</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +977,26 @@
       <c r="D13" t="n">
         <v>1480</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>189</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>45</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1013,34 @@
       <c r="D14" t="n">
         <v>1860</v>
       </c>
-      <c r="E14" t="n">
-        <v>292</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>222</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>191</v>
+      </c>
+      <c r="J14" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1057,42 @@
       <c r="D15" t="n">
         <v>4728</v>
       </c>
-      <c r="E15" t="n">
-        <v>877</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>413</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="G15" t="n">
+        <v>34</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>115</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>352</v>
+      </c>
+      <c r="M15" t="n">
+        <v>45</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1109,18 @@
       <c r="D16" t="n">
         <v>2984</v>
       </c>
-      <c r="E16" t="n">
-        <v>240</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1137,26 @@
       <c r="D17" t="n">
         <v>2228</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>329</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>34</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1173,34 @@
       <c r="D18" t="n">
         <v>1704</v>
       </c>
-      <c r="E18" t="n">
-        <v>248</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>241</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>207</v>
+      </c>
+      <c r="J18" t="n">
+        <v>29</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1217,18 @@
       <c r="D19" t="n">
         <v>1612</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1245,26 @@
       <c r="D20" t="n">
         <v>3904</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>368</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>45</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1281,34 @@
       <c r="D21" t="n">
         <v>2804</v>
       </c>
-      <c r="E21" t="n">
-        <v>582</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>424</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="G21" t="n">
+        <v>29</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>322</v>
+      </c>
+      <c r="J21" t="n">
+        <v>45</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
